--- a/fixtures/xlsx/path-many-rows/input.xlsx
+++ b/fixtures/xlsx/path-many-rows/input.xlsx
@@ -10,160 +10,160 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
+    <t>row 19</t>
+  </si>
+  <si>
+    <t>row 13</t>
+  </si>
+  <si>
+    <t>row 15</t>
+  </si>
+  <si>
+    <t>row 20</t>
+  </si>
+  <si>
+    <t>row 28</t>
+  </si>
+  <si>
+    <t>row 34</t>
+  </si>
+  <si>
+    <t>row 35</t>
+  </si>
+  <si>
+    <t>row 39</t>
+  </si>
+  <si>
+    <t>row 31</t>
+  </si>
+  <si>
+    <t>row 4</t>
+  </si>
+  <si>
+    <t>row 29</t>
+  </si>
+  <si>
+    <t>row 1</t>
+  </si>
+  <si>
+    <t>row 8</t>
+  </si>
+  <si>
+    <t>row 23</t>
+  </si>
+  <si>
+    <t>row 11</t>
+  </si>
+  <si>
+    <t>row 7</t>
+  </si>
+  <si>
+    <t>row 49</t>
+  </si>
+  <si>
+    <t>row 24</t>
+  </si>
+  <si>
+    <t>row 43</t>
+  </si>
+  <si>
+    <t>row 22</t>
+  </si>
+  <si>
+    <t>row 30</t>
+  </si>
+  <si>
+    <t>row 27</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>row 6</t>
+  </si>
+  <si>
+    <t>row 36</t>
+  </si>
+  <si>
+    <t>row 25</t>
+  </si>
+  <si>
+    <t>row 50</t>
+  </si>
+  <si>
+    <t>row 10</t>
+  </si>
+  <si>
+    <t>row 37</t>
+  </si>
+  <si>
+    <t>row 18</t>
+  </si>
+  <si>
+    <t>row 44</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>row 45</t>
+  </si>
+  <si>
+    <t>row 47</t>
+  </si>
+  <si>
+    <t>row 2</t>
+  </si>
+  <si>
+    <t>row 32</t>
+  </si>
+  <si>
+    <t>row 40</t>
+  </si>
+  <si>
+    <t>row 9</t>
+  </si>
+  <si>
+    <t>row 42</t>
+  </si>
+  <si>
+    <t>row 46</t>
+  </si>
+  <si>
+    <t>row 14</t>
+  </si>
+  <si>
+    <t>row 26</t>
+  </si>
+  <si>
+    <t>row 3</t>
+  </si>
+  <si>
+    <t>row 41</t>
+  </si>
+  <si>
+    <t>row 5</t>
+  </si>
+  <si>
+    <t>row 38</t>
+  </si>
+  <si>
+    <t>row 17</t>
+  </si>
+  <si>
+    <t>row 33</t>
+  </si>
+  <si>
+    <t>row 21</t>
+  </si>
+  <si>
     <t>row 48</t>
   </si>
   <si>
-    <t>row 29</t>
-  </si>
-  <si>
-    <t>row 15</t>
-  </si>
-  <si>
-    <t>row 21</t>
-  </si>
-  <si>
-    <t>row 33</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>row 7</t>
-  </si>
-  <si>
-    <t>row 5</t>
-  </si>
-  <si>
-    <t>row 18</t>
-  </si>
-  <si>
-    <t>row 22</t>
-  </si>
-  <si>
-    <t>row 4</t>
-  </si>
-  <si>
-    <t>row 36</t>
-  </si>
-  <si>
-    <t>row 34</t>
-  </si>
-  <si>
-    <t>row 38</t>
-  </si>
-  <si>
-    <t>row 49</t>
-  </si>
-  <si>
-    <t>row 40</t>
-  </si>
-  <si>
-    <t>row 30</t>
-  </si>
-  <si>
-    <t>row 2</t>
-  </si>
-  <si>
-    <t>row 6</t>
-  </si>
-  <si>
-    <t>row 39</t>
-  </si>
-  <si>
-    <t>row 14</t>
-  </si>
-  <si>
-    <t>row 25</t>
-  </si>
-  <si>
-    <t>row 37</t>
-  </si>
-  <si>
-    <t>row 3</t>
-  </si>
-  <si>
-    <t>row 10</t>
-  </si>
-  <si>
-    <t>row 42</t>
-  </si>
-  <si>
-    <t>Index</t>
-  </si>
-  <si>
-    <t>row 8</t>
-  </si>
-  <si>
-    <t>row 20</t>
-  </si>
-  <si>
-    <t>row 27</t>
-  </si>
-  <si>
-    <t>row 11</t>
-  </si>
-  <si>
-    <t>row 43</t>
+    <t>row 12</t>
   </si>
   <si>
     <t>row 16</t>
-  </si>
-  <si>
-    <t>row 32</t>
-  </si>
-  <si>
-    <t>row 41</t>
-  </si>
-  <si>
-    <t>row 24</t>
-  </si>
-  <si>
-    <t>row 13</t>
-  </si>
-  <si>
-    <t>row 23</t>
-  </si>
-  <si>
-    <t>row 44</t>
-  </si>
-  <si>
-    <t>row 9</t>
-  </si>
-  <si>
-    <t>row 45</t>
-  </si>
-  <si>
-    <t>row 46</t>
-  </si>
-  <si>
-    <t>row 47</t>
-  </si>
-  <si>
-    <t>row 26</t>
-  </si>
-  <si>
-    <t>row 28</t>
-  </si>
-  <si>
-    <t>row 50</t>
-  </si>
-  <si>
-    <t>row 12</t>
-  </si>
-  <si>
-    <t>row 1</t>
-  </si>
-  <si>
-    <t>row 19</t>
-  </si>
-  <si>
-    <t>row 31</t>
-  </si>
-  <si>
-    <t>row 17</t>
-  </si>
-  <si>
-    <t>row 35</t>
   </si>
 </sst>
 </file>
@@ -173,10 +173,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2">
@@ -184,7 +184,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -192,7 +192,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
@@ -200,7 +200,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
@@ -208,7 +208,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -216,7 +216,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -224,7 +224,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -232,7 +232,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -240,7 +240,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -248,7 +248,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
@@ -256,7 +256,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -264,7 +264,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -272,7 +272,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
@@ -280,7 +280,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -288,7 +288,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16">
@@ -304,7 +304,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -312,7 +312,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19">
@@ -320,7 +320,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20">
@@ -328,7 +328,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -336,7 +336,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -344,7 +344,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -352,7 +352,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -360,7 +360,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
@@ -368,7 +368,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
@@ -376,7 +376,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27">
@@ -384,7 +384,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28">
@@ -392,7 +392,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
@@ -400,7 +400,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -408,7 +408,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -416,7 +416,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
@@ -424,7 +424,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
@@ -432,7 +432,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34">
@@ -440,7 +440,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35">
@@ -448,7 +448,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -456,7 +456,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>51</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -464,7 +464,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38">
@@ -472,7 +472,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39">
@@ -480,7 +480,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40">
@@ -488,7 +488,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
@@ -496,7 +496,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
     </row>
     <row r="42">
@@ -504,7 +504,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43">
@@ -512,7 +512,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44">
@@ -520,7 +520,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45">
@@ -528,7 +528,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46">
@@ -536,7 +536,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47">
@@ -544,7 +544,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48">
@@ -552,7 +552,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49">
@@ -560,7 +560,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50">
@@ -568,7 +568,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51">
@@ -576,7 +576,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/fixtures/xlsx/path-many-rows/input.xlsx
+++ b/fixtures/xlsx/path-many-rows/input.xlsx
@@ -10,160 +10,160 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
+    <t>row 9</t>
+  </si>
+  <si>
+    <t>row 11</t>
+  </si>
+  <si>
+    <t>row 16</t>
+  </si>
+  <si>
+    <t>row 50</t>
+  </si>
+  <si>
+    <t>row 13</t>
+  </si>
+  <si>
+    <t>row 48</t>
+  </si>
+  <si>
+    <t>row 42</t>
+  </si>
+  <si>
     <t>row 19</t>
   </si>
   <si>
-    <t>row 13</t>
+    <t>row 36</t>
+  </si>
+  <si>
+    <t>row 10</t>
+  </si>
+  <si>
+    <t>row 38</t>
+  </si>
+  <si>
+    <t>row 41</t>
+  </si>
+  <si>
+    <t>row 46</t>
   </si>
   <si>
     <t>row 15</t>
   </si>
   <si>
+    <t>row 29</t>
+  </si>
+  <si>
+    <t>row 37</t>
+  </si>
+  <si>
+    <t>Index</t>
+  </si>
+  <si>
+    <t>row 45</t>
+  </si>
+  <si>
+    <t>row 22</t>
+  </si>
+  <si>
+    <t>row 24</t>
+  </si>
+  <si>
+    <t>row 32</t>
+  </si>
+  <si>
+    <t>row 5</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>row 26</t>
+  </si>
+  <si>
+    <t>row 8</t>
+  </si>
+  <si>
+    <t>row 34</t>
+  </si>
+  <si>
+    <t>row 4</t>
+  </si>
+  <si>
+    <t>row 21</t>
+  </si>
+  <si>
+    <t>row 25</t>
+  </si>
+  <si>
+    <t>row 6</t>
+  </si>
+  <si>
+    <t>row 3</t>
+  </si>
+  <si>
+    <t>row 14</t>
+  </si>
+  <si>
+    <t>row 17</t>
+  </si>
+  <si>
+    <t>row 47</t>
+  </si>
+  <si>
+    <t>row 43</t>
+  </si>
+  <si>
+    <t>row 35</t>
+  </si>
+  <si>
+    <t>row 1</t>
+  </si>
+  <si>
+    <t>row 7</t>
+  </si>
+  <si>
+    <t>row 44</t>
+  </si>
+  <si>
+    <t>row 30</t>
+  </si>
+  <si>
+    <t>row 23</t>
+  </si>
+  <si>
+    <t>row 33</t>
+  </si>
+  <si>
+    <t>row 39</t>
+  </si>
+  <si>
+    <t>row 12</t>
+  </si>
+  <si>
+    <t>row 27</t>
+  </si>
+  <si>
+    <t>row 28</t>
+  </si>
+  <si>
+    <t>row 31</t>
+  </si>
+  <si>
+    <t>row 2</t>
+  </si>
+  <si>
     <t>row 20</t>
   </si>
   <si>
-    <t>row 28</t>
-  </si>
-  <si>
-    <t>row 34</t>
-  </si>
-  <si>
-    <t>row 35</t>
-  </si>
-  <si>
-    <t>row 39</t>
-  </si>
-  <si>
-    <t>row 31</t>
-  </si>
-  <si>
-    <t>row 4</t>
-  </si>
-  <si>
-    <t>row 29</t>
-  </si>
-  <si>
-    <t>row 1</t>
-  </si>
-  <si>
-    <t>row 8</t>
-  </si>
-  <si>
-    <t>row 23</t>
-  </si>
-  <si>
-    <t>row 11</t>
-  </si>
-  <si>
-    <t>row 7</t>
-  </si>
-  <si>
     <t>row 49</t>
   </si>
   <si>
-    <t>row 24</t>
-  </si>
-  <si>
-    <t>row 43</t>
-  </si>
-  <si>
-    <t>row 22</t>
-  </si>
-  <si>
-    <t>row 30</t>
-  </si>
-  <si>
-    <t>row 27</t>
-  </si>
-  <si>
-    <t>Index</t>
-  </si>
-  <si>
-    <t>row 6</t>
-  </si>
-  <si>
-    <t>row 36</t>
-  </si>
-  <si>
-    <t>row 25</t>
-  </si>
-  <si>
-    <t>row 50</t>
-  </si>
-  <si>
-    <t>row 10</t>
-  </si>
-  <si>
-    <t>row 37</t>
+    <t>row 40</t>
   </si>
   <si>
     <t>row 18</t>
-  </si>
-  <si>
-    <t>row 44</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>row 45</t>
-  </si>
-  <si>
-    <t>row 47</t>
-  </si>
-  <si>
-    <t>row 2</t>
-  </si>
-  <si>
-    <t>row 32</t>
-  </si>
-  <si>
-    <t>row 40</t>
-  </si>
-  <si>
-    <t>row 9</t>
-  </si>
-  <si>
-    <t>row 42</t>
-  </si>
-  <si>
-    <t>row 46</t>
-  </si>
-  <si>
-    <t>row 14</t>
-  </si>
-  <si>
-    <t>row 26</t>
-  </si>
-  <si>
-    <t>row 3</t>
-  </si>
-  <si>
-    <t>row 41</t>
-  </si>
-  <si>
-    <t>row 5</t>
-  </si>
-  <si>
-    <t>row 38</t>
-  </si>
-  <si>
-    <t>row 17</t>
-  </si>
-  <si>
-    <t>row 33</t>
-  </si>
-  <si>
-    <t>row 21</t>
-  </si>
-  <si>
-    <t>row 48</t>
-  </si>
-  <si>
-    <t>row 12</t>
-  </si>
-  <si>
-    <t>row 16</t>
   </si>
 </sst>
 </file>
@@ -173,10 +173,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
         <v>22</v>
-      </c>
-      <c r="B1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2">
@@ -184,7 +184,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -192,7 +192,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -200,7 +200,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -208,7 +208,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -216,7 +216,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -224,7 +224,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -232,7 +232,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
@@ -240,7 +240,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -248,7 +248,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -256,7 +256,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -264,7 +264,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -272,7 +272,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14">
@@ -280,7 +280,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -288,7 +288,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
@@ -296,7 +296,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
@@ -304,7 +304,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -312,7 +312,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
@@ -320,7 +320,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20">
@@ -328,7 +328,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -336,7 +336,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22">
@@ -344,7 +344,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
@@ -352,7 +352,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -360,7 +360,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25">
@@ -368,7 +368,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
@@ -376,7 +376,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27">
@@ -384,7 +384,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
@@ -392,7 +392,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29">
@@ -400,7 +400,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30">
@@ -408,7 +408,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
@@ -416,7 +416,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32">
@@ -424,7 +424,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33">
@@ -432,7 +432,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -440,7 +440,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35">
@@ -448,7 +448,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36">
@@ -456,7 +456,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37">
@@ -464,7 +464,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38">
@@ -472,7 +472,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39">
@@ -480,7 +480,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
@@ -488,7 +488,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41">
@@ -496,7 +496,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42">
@@ -504,7 +504,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43">
@@ -512,7 +512,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
@@ -520,7 +520,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
     </row>
     <row r="45">
@@ -528,7 +528,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="46">
@@ -536,7 +536,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47">
@@ -544,7 +544,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48">
@@ -560,7 +560,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -568,7 +568,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51">
@@ -576,7 +576,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
